--- a/public/track-trace-template.xlsx
+++ b/public/track-trace-template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">Item Name</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">SL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight</t>
   </si>
 </sst>
 </file>
@@ -476,7 +479,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
@@ -526,6 +529,9 @@
       </c>
       <c r="M1" s="4" t="s">
         <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
